--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -457,25 +457,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -494,16 +494,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7174576970697483</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5470746614782933</v>
+        <v>0.7174593192359091</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5909090909090908</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3470864532358549</v>
+        <v>0.547063910069963</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2769962462905096</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -653,25 +653,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2265957446808511</v>
+        <v>0.3470953541388256</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2178173456753729</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -709,25 +709,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1243794587583279</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -798,38 +798,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1114</v>
+        <v>41873</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -839,32 +839,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>OPPORTUNITY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1114</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -874,38 +880,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Engineering Course for Beginners</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1133434</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7174576970697483</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -915,26 +915,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+          <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79875</v>
+        <v>1133477</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -942,11 +942,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5470746614782933</v>
+        <v>0.7174593192359091</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -961,21 +961,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data", 30 views). Your angle: claim the space — straightforward, solid coverage of "Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)", 1.3M views). Your angle: claim the space — straightforward, solid coverage of "what is data pipeline" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>1260783</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5909090909090908</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>619941</v>
+        <v>79875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3470864532358549</v>
+        <v>0.547063910069963</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1038,26 +1038,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data", 30 views). Your angle: claim the space — straightforward, solid coverage of "Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>16539261</v>
+        <v>30</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1065,11 +1065,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2769962462905096</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1084,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "Open-sourced jev architecture last year with model,paper and dataset" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>airbytehq/airbyte</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Airbyte 2.0: Enterprise Flex</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>619941</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.2265957446808511</v>
+        <v>0.3470953541388256</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1119,33 +1125,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>7655693</v>
-      </c>
+          <t>data engineering</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.2178173456753729</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1155,38 +1155,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "what is data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>John Cooper Clarke - Evidently Chickentown</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2001363</v>
-      </c>
+          <t>what is data engineering</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1243794587583279</v>
+        <v>0.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,25 +1236,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1264,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1279,16 +1273,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1292,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,7 +1301,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7174576970697483</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1316,7 +1310,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1320,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1335,7 +1329,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5470746614782933</v>
+        <v>0.7174593192359091</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1344,7 +1338,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1348,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1363,16 +1357,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5909090909090908</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1382,16 +1376,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3470864532358549</v>
+        <v>0.547063910069963</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1400,7 +1394,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1404,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,16 +1413,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2769962462905096</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1432,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2265957446808511</v>
+        <v>0.3470953541388256</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1466,25 +1460,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2178173456753729</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1494,25 +1488,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1243794587583279</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1522,25 +1516,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1090187292415935</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1544,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1559,16 +1553,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1078552758288623</v>
+        <v>0.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1578,16 +1572,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09634652044887292</v>
+        <v>0.2769908026098577</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1596,7 +1590,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1606,25 +1600,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07556158245386475</v>
+        <v>0.2696969696969697</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1628,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06100269245130988</v>
+        <v>0.2393939393939394</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1656,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05312579840025156</v>
+        <v>0.2363636363636363</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1684,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,16 +1693,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.05153784171530767</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1712,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1727,16 +1721,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.0482361495980976</v>
+        <v>0.2297872340425532</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1746,16 +1740,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.0406894247587603</v>
+        <v>0.2178130650106124</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1764,7 +1758,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1768,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,16 +1777,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.03789084763083938</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1796,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1811,16 +1805,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.0376392901361948</v>
+        <v>0.2060606060606061</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1830,25 +1824,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.02914922469194034</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -1858,25 +1852,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.02808010533970089</v>
+        <v>0.1575757575757576</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -1886,25 +1880,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.02690092958355443</v>
+        <v>0.1545454545454545</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -1914,25 +1908,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.02606764538254427</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -1942,25 +1936,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.02485702493956725</v>
+        <v>0.1454545454545454</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -1970,25 +1964,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.02103649548965273</v>
+        <v>0.1424242424242424</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1992,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,7 +2001,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.01962148458227699</v>
+        <v>0.1243770143856615</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2016,7 +2010,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2020,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2035,16 +2029,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.01132008725900596</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2048,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2063,16 +2057,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.009967965725291355</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2082,25 +2076,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.009401961362341059</v>
+        <v>0.1121212121212121</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2104,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2119,7 +2113,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.007216555627616296</v>
+        <v>0.109016586746325</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2128,7 +2122,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2132,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2147,16 +2141,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.1078531561984121</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2160,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2175,16 +2169,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.103030303030303</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2188,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2203,16 +2197,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.09696969696969697</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2216,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2231,7 +2225,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.005377041448027829</v>
+        <v>0.09634462699473312</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2240,7 +2234,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2244,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,16 +2253,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.003411748521117072</v>
+        <v>0.09393939393939395</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2287,16 +2281,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.003191489361702127</v>
+        <v>0.09393939393939395</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2300,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2315,16 +2309,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.002735687754259773</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2328,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2343,16 +2337,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.002012459957156614</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2356,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2371,16 +2365,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.001933848240080184</v>
+        <v>0.0818181818181818</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2384,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2399,16 +2393,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.001729457775681465</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2412,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2427,7 +2421,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.001650846058605035</v>
+        <v>0.07557581951104474</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2436,7 +2430,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2440,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2455,16 +2449,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.001525067311282747</v>
+        <v>0.07272727272727272</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2468,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2483,16 +2477,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.001509344967867461</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2496,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2511,16 +2505,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.001462177937621603</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -2530,25 +2524,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.001257787473222884</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2552,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,16 +2561,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.001257787473222884</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2580,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2595,16 +2589,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.001242065129807598</v>
+        <v>0.06363636363636363</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2608,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2623,16 +2617,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.00119489809956174</v>
+        <v>0.06363636363636363</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2636,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2651,16 +2645,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.001163453412731168</v>
+        <v>0.06363636363636363</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2664,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2679,7 +2673,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.001021952321993593</v>
+        <v>0.06100149359327098</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2688,7 +2682,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2692,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2707,16 +2701,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0007703948273490164</v>
+        <v>0.0606060606060606</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -2726,25 +2720,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.0005817267063655838</v>
+        <v>0.05454545454545454</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2748,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2763,16 +2757,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0004716703024585814</v>
+        <v>0.05454545454545454</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2776,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2785,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0004559479590432955</v>
+        <v>0.05312475434321201</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2794,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2804,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2819,7 +2813,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0003773362419668652</v>
+        <v>0.05153682886565522</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2828,7 +2822,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2832,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>power bi download desktop</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,16 +2841,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.000330169211721007</v>
+        <v>0.05151515151515151</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2860,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2875,16 +2869,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0002830021814751489</v>
+        <v>0.04848484848484848</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2888,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2903,16 +2897,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0001729457775681465</v>
+        <v>0.04848484848484848</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2916,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,7 +2925,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0001257787473222884</v>
+        <v>0.04823520163509158</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2940,7 +2934,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2944,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2959,16 +2953,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0001100564039070023</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -2978,25 +2972,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.572234341528605e-05</v>
+        <v>0.04242424242424242</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3000,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3015,7 +3009,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>0.04068862510808899</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3024,7 +3018,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3028,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3043,7 +3037,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.03789010297932553</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3052,7 +3046,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3056,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3071,16 +3065,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>0.03763855042842544</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -3090,25 +3084,1873 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>data engineering consulting</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>data engineering courses</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>data scientist</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>dbt</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EVERGREEN</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>google analytics</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.02914865183554752</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>dbt-labs/dbt-utils</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.02807955349422216</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>google data analytics professional certificate</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.02727272727272727</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hiflylabs/awesome-dbt</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.026900400911878</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Multiwoven/multiwoven</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.02606713308702146</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://github.com/Multiwoven/multiwoven</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kaelio/ktx</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.0248565364358148</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://github.com/Kaelio/ktx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>duckdb/dbt-duckdb</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.02103608206901973</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>astronomer/astronomer-cosmos</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01962109897020674</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>snowflake data engineering</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>python for data engineering</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>dbt data engineering</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>google data analytics certification</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01212121212121212</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>mikehasa/agentacct</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01131986479050389</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://github.com/mikehasa/agentacct</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>zhongyu09/openchatbi</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.009967769829415926</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://github.com/zhongyu09/openchatbi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TimeCopilot/timecopilot</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.009401776589890732</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>data pipeline development</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.00909090909090909</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.007216413803946231</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.006382978723404255</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.006382978723404255</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://sentralis.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.006382978723404255</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>data pipeline tools</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.006060606060606061</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>upgini/upgini</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.005376935775489349</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://github.com/upgini/upgini</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AngusKit/AngusKit</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.003411681471582423</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://github.com/AngusKit/AngusKit</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>We Benchmark Analytics Agents, this explains how</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.003191489361702127</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dbt analytics engineering certification</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>big data pipeline</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>data pipeline architecture</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>data pipeline platform</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>data pipeline aws</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>data pipeline meaning</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>data pipeline monitoring</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cesarjoquin/Marketing-Skills</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.00273563399103844</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>colossus-lab/openarg_backend</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.002012420407200692</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.001933810235044415</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>surfalytics/data-projects</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.001729423787438095</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://github.com/surfalytics/data-projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chrisinho8/DACH-data-job-market</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.001650813615281818</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>decisionbox-io/decisionbox-platform</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.001525037339831774</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>docwire/docwire</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.001509315305400519</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://github.com/docwire/docwire</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Shaf2665/Hermes-router</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.001462149202106753</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ellie886/Datalume</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.001257762754500433</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://github.com/ellie886/Datalume</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>marieai/marie-ai</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.001257762754500433</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://github.com/marieai/marie-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ESIPFed/Geoweaver</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.001242040720069177</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ServiceNow/SyGra</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.001194874616775411</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://github.com/ServiceNow/SyGra</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>social-media-skills/skills</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.0011634305479129</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://github.com/social-media-skills/skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>agentscope-ai/QwenPaw-Data</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.001021932238031601</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0007703796871315148</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Priyanshu-byte-coder/contextrot</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.00058171527395645</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0004716610329376621</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>pella-labs/pellametric</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.0004559389985064068</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://github.com/pella-labs/pellametric</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.0003773288263501297</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.0003301627230563635</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.0002829966197625973</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.0001729423787438095</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.0001257762754500433</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0.0001100542410187878</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1.572203443125541e-05</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>etl data pipeline</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>power bi para que sirve</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
         <v>0</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>hn</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -3123,7 +4965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A247"/>
+  <dimension ref="A1:A249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3633,63 +5475,63 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analytics entry level jobs</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>data analytics internship</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics jobs remote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
@@ -3710,56 +5552,56 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
@@ -3780,14 +5622,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
@@ -3808,1048 +5650,1062 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>data pipeline station</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi course</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
+        <is>
+          <t>why power bi over excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,16 +466,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -485,25 +485,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7174593192359091</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5909090909090908</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.547063910069963</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -625,25 +625,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -653,16 +653,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3470953541388256</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -709,25 +709,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -803,21 +803,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Avoiding circular dependency errors in DAX</t>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>41873</v>
+        <v>16539891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -839,38 +839,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1114</v>
+        <v>619941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Fast wavedash on pad (Lightdash handcam)" has 48.8k views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>lightdash/lightdash</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fast wavedash on pad (Lightdash handcam)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>48791</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -905,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -915,38 +921,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Engineering Course for Beginners</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1133477</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7174593192359091</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -961,21 +961,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)", 1.3M views). Your angle: claim the space — straightforward, solid coverage of "what is data pipeline" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)</t>
+          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1260783</v>
+        <v>7656650</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5909090909090908</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("ClearML Introduction", 319.8k views). Your angle: claim the space — straightforward, solid coverage of "clearml/clearml" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+          <t>ClearML Introduction</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>79875</v>
+        <v>319846</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.547063910069963</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1038,38 +1038,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data", 30 views). Your angle: claim the space — straightforward, solid coverage of "Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data" has almost no competition right now.</t>
+          <t>REVISIT — "I suspect someone is playing tricks, but I have no evidence" has 364.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>I suspect someone is playing tricks, but I have no evidence</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>364126461</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1079,38 +1079,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
+          <t>John Cooper Clarke - Evidently Chickentown</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>619941</v>
+        <v>2001414</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3470953541388256</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1125,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data engineering</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>langfuse/langfuse</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>79875</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1155,32 +1161,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "what is data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Engineering Course for Beginners</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1133490</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1248,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1245,16 +1257,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1264,25 +1276,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1304,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1310,7 +1322,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1332,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1329,7 +1341,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7174593192359091</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1338,7 +1350,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1360,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1357,16 +1369,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5909090909090908</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1376,16 +1388,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.547063910069963</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1394,7 +1406,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1404,25 +1416,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1432,16 +1444,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3470953541388256</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1450,7 +1462,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1472,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1469,16 +1481,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1488,25 +1500,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1516,25 +1528,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.772</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1556,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1553,16 +1565,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>0.62336</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1584,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2769908026098577</v>
+        <v>0.5655</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1600,25 +1612,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2696969696969697</v>
+        <v>0.5432</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1628,25 +1640,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2393939393939394</v>
+        <v>0.5270400000000001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1656,25 +1668,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2363636363636363</v>
+        <v>0.49344</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1696,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1693,16 +1705,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.4192</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1724,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1721,16 +1733,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2297872340425532</v>
+        <v>0.3881600000000001</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1740,16 +1752,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2178130650106124</v>
+        <v>0.3856</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1758,7 +1770,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1768,16 +1780,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.36</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1786,7 +1798,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1808,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1805,16 +1817,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2060606060606061</v>
+        <v>0.2992</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -1824,25 +1836,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.28832</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1864,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1575757575757576</v>
+        <v>0.27632</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -1880,25 +1892,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1545454545454545</v>
+        <v>0.26784</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -1908,25 +1920,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.25552</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1948,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1945,7 +1957,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.2412</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1973,16 +1985,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1424242424242424</v>
+        <v>0.234</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2004,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2001,7 +2013,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.1243770143856615</v>
+        <v>0.21664</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2010,7 +2022,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2032,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2029,16 +2041,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.20224</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2048,16 +2060,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.1182</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2066,7 +2078,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2076,25 +2088,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1121212121212121</v>
+        <v>0.11776</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2116,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2113,16 +2125,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.109016586746325</v>
+        <v>0.1095</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2144,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2141,7 +2153,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1078531561984121</v>
+        <v>0.104</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2150,7 +2162,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2169,16 +2181,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.103030303030303</v>
+        <v>0.09824000000000001</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2197,16 +2209,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.09696969696969697</v>
+        <v>0.07600000000000001</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -2216,25 +2228,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.09634462699473312</v>
+        <v>0.06</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2256,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2253,7 +2265,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2262,7 +2274,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2272,16 +2284,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.06</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2290,7 +2302,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2312,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2309,16 +2321,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.05728</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -2328,16 +2340,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.054</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2346,7 +2358,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2356,16 +2368,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.048</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2374,7 +2386,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2396,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.0474</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2402,7 +2414,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2412,25 +2424,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.07557581951104474</v>
+        <v>0.0474</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2452,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2449,7 +2461,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.0456</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2458,7 +2470,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2480,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2477,7 +2489,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2486,7 +2498,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2508,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2505,7 +2517,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.0414</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2514,7 +2526,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2524,25 +2536,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.03728</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2564,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>power bi report</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2561,7 +2573,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.0336</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2570,7 +2582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
         </is>
       </c>
     </row>
@@ -2580,16 +2592,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.0336</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2598,7 +2610,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2608,16 +2620,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2626,7 +2638,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -2636,16 +2648,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.0312</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2654,7 +2666,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2676,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2673,7 +2685,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.06100149359327098</v>
+        <v>0.0304</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2682,7 +2694,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -2692,16 +2704,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.0294</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2710,7 +2722,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2732,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2729,7 +2741,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.0288</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2738,7 +2750,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2760,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2757,7 +2769,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.0276</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2766,7 +2778,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2785,16 +2797,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.05312475434321201</v>
+        <v>0.0246</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2816,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2813,16 +2825,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.05153682886565522</v>
+        <v>0.0246</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2844,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>power bi download desktop</t>
+          <t>data analytics software</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2841,7 +2853,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.05151515151515151</v>
+        <v>0.024</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2850,7 +2862,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2872,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>power bi free</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2869,7 +2881,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.0234</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2878,7 +2890,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2900,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>data science and engineering</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2897,7 +2909,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.0234</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2906,7 +2918,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=data+science+and+engineering</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2928,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2925,7 +2937,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.04823520163509158</v>
+        <v>0.02304</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2934,7 +2946,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -2944,16 +2956,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi web</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.0228</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2962,7 +2974,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2972,25 +2984,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.04242424242424242</v>
+        <v>0.02224</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>social engineering</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3009,16 +3021,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.04068862510808899</v>
+        <v>0.021</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3040,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3037,7 +3049,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.03789010297932553</v>
+        <v>0.02016</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3046,7 +3058,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3068,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3065,16 +3077,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.03763855042842544</v>
+        <v>0.0198</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3093,16 +3105,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01936</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -3112,16 +3124,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0192</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3130,7 +3142,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3149,7 +3161,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0192</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3158,7 +3170,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3168,16 +3180,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0186</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3186,7 +3198,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3208,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3205,7 +3217,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0186</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3214,7 +3226,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3233,7 +3245,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.02914865183554752</v>
+        <v>0.01808</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3242,7 +3254,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3264,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3261,7 +3273,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.02807955349422216</v>
+        <v>0.01792</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3270,7 +3282,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3292,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3289,16 +3301,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.02727272727272727</v>
+        <v>0.01744</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3317,16 +3329,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.026900400911878</v>
+        <v>0.0168</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3345,16 +3357,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.02606713308702146</v>
+        <v>0.0156</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3364,25 +3376,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0248565364358148</v>
+        <v>0.0156</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3401,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.02103608206901973</v>
+        <v>0.01536</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3410,7 +3422,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3432,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3429,7 +3441,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.01962109897020674</v>
+        <v>0.01536</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3438,7 +3450,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3460,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3457,16 +3469,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.01818181818181818</v>
+        <v>0.0152</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3488,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3485,7 +3497,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.015</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3494,7 +3506,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3516,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3513,16 +3525,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01472</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3544,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3541,7 +3553,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.0144</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3550,7 +3562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3572,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3569,16 +3581,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.01131986479050389</v>
+        <v>0.0144</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3600,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3597,7 +3609,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.009967769829415926</v>
+        <v>0.0144</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3606,7 +3618,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3628,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3625,16 +3637,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.009401776589890732</v>
+        <v>0.0132</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3653,7 +3665,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.0132</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3662,7 +3674,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3684,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3681,7 +3693,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.007216413803946231</v>
+        <v>0.01296</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3690,7 +3702,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3712,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3709,16 +3721,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.0126</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3740,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3737,16 +3749,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.0114</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3768,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>download power bi desktop</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3765,16 +3777,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.0108</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -3784,25 +3796,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.0104</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3824,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3821,16 +3833,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.005376935775489349</v>
+        <v>0.0102</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3852,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3849,16 +3861,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.003411681471582423</v>
+        <v>0.0102</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3880,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>data analytics consulting</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3877,16 +3889,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.003191489361702127</v>
+        <v>0.0102</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3908,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>data engineering tools</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3905,7 +3917,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3914,7 +3926,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3936,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3933,7 +3945,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3942,7 +3954,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -3952,16 +3964,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>feature engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3970,7 +3982,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=feature+engineering</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3992,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3989,16 +4001,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.00848</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4020,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4017,16 +4029,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.00736</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4036,16 +4048,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.0072</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4054,7 +4066,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4076,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4073,16 +4085,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.0072</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4092,25 +4104,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.00273563399103844</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4132,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4129,7 +4141,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.002012420407200692</v>
+        <v>0.0064</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4138,7 +4150,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4160,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4157,16 +4169,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.001933810235044415</v>
+        <v>0.006</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4188,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4185,16 +4197,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.001729423787438095</v>
+        <v>0.006</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4216,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4213,7 +4225,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.001650813615281818</v>
+        <v>0.005920000000000001</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4222,7 +4234,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4244,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4241,7 +4253,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.001525037339831774</v>
+        <v>0.00544</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4250,7 +4262,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4272,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>what is big data analytics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4269,16 +4281,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.001509315305400519</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4300,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>masters in data analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4297,16 +4309,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.001462149202106753</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4328,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>coursera</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,16 +4337,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.001257762754500433</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=coursera</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4356,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4353,16 +4365,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.001257762754500433</v>
+        <v>0.0045</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4384,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4381,16 +4393,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.001242040720069177</v>
+        <v>0.0045</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4409,7 +4421,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.001194874616775411</v>
+        <v>0.00432</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4418,7 +4430,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>exmergo/dex</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,7 +4449,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0011634305479129</v>
+        <v>0.00384</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/exmergo/dex</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4468,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4465,7 +4477,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.001021932238031601</v>
+        <v>0.00368</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4474,7 +4486,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4493,16 +4505,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0007703796871315148</v>
+        <v>0.0036</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4524,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4521,16 +4533,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.00058171527395645</v>
+        <v>0.003</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4552,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4549,16 +4561,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.0004716610329376621</v>
+        <v>0.003</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4580,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>Dreamerol/ALLSTATS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4577,7 +4589,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0004559389985064068</v>
+        <v>0.00272</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4586,7 +4598,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4608,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>Codpal-Limited/deckgauge</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4605,7 +4617,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0003773288263501297</v>
+        <v>0.00256</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4636,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>errajeshcs-pixel/DS4Earth</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4633,7 +4645,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0003301627230563635</v>
+        <v>0.00256</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4642,7 +4654,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4664,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4661,16 +4673,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0002829966197625973</v>
+        <v>0.0024</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -4680,25 +4692,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0001729423787438095</v>
+        <v>0.0018</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4720,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4717,16 +4729,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0001257762754500433</v>
+        <v>0.0015</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4748,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4745,16 +4757,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0001100542410187878</v>
+        <v>0.0015</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4776,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4773,16 +4785,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1.572203443125541e-05</v>
+        <v>0.0012</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4804,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4801,16 +4813,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4820,25 +4832,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4860,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4857,7 +4869,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4866,91 +4878,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>power bi para que sirve</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A249"/>
+  <dimension ref="A1:A246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5475,63 +5403,63 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>data analytics entry level jobs</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>data analytics internship</t>
+          <t>data analytics google certification</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics internships</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>data analytics jobs remote</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics meaning</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics vs data science</t>
         </is>
       </c>
     </row>
@@ -5552,56 +5480,56 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>data engineering certification</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering manager</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>data engineering salary</t>
+          <t>data engineering system design</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering things</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>data engineering vs data science</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
@@ -5622,14 +5550,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data pipeline architecture diagram</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>data pipeline engineer</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
@@ -5650,1062 +5578,1041 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>data pipeline orchestration</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>data pipeline station</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi courses</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>power bi report builder</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
-        <is>
-          <t>why power bi is used</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>why power bi over excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>why power bi over tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -503,7 +503,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -597,25 +597,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -625,25 +625,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.5655</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -653,16 +653,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -709,16 +709,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.31708</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -798,26 +798,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16539891</v>
+        <v>619941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -839,30 +839,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
+          <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>619941</v>
+        <v>1133491</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -880,30 +880,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REVISIT — "Fast wavedash on pad (Lightdash handcam)" has 48.8k views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fast wavedash on pad (Lightdash handcam)</t>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>48791</v>
+        <v>79875</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -956,26 +956,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7656650</v>
+        <v>16540035</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -997,38 +997,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("ClearML Introduction", 319.8k views). Your angle: claim the space — straightforward, solid coverage of "clearml/clearml" has almost no competition right now.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ClearML Introduction</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>319846</v>
+        <v>41873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1038,38 +1038,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>OPPORTUNITY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "I suspect someone is playing tricks, but I have no evidence" has 364.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I suspect someone is playing tricks, but I have no evidence</t>
+          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>364126461</v>
+        <v>1114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.5655</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1079,38 +1079,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>John Cooper Clarke - Evidently Chickentown</t>
+          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2001414</v>
+        <v>7656832</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1125,33 +1125,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>79875</v>
-      </c>
+          <t>data engineering</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1166,33 +1160,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Engineering Course for Beginners</t>
+          <t>John Cooper Clarke - Evidently Chickentown</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1133490</v>
+        <v>2001417</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0.31708</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,7 +1242,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1257,7 +1251,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1266,7 +1260,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1270,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1294,7 +1288,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1298,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1322,7 +1316,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1354,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1369,7 +1363,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1378,7 +1372,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1388,25 +1382,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1416,25 +1410,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.5655</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1444,16 +1438,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1462,7 +1456,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1466,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1481,16 +1475,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1500,16 +1494,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.31708</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1518,7 +1512,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1522,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1537,16 +1531,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.772</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1550,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1565,7 +1559,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62336</v>
+        <v>0.278</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1574,7 +1568,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1584,25 +1578,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5655</v>
+        <v>0.27504</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1606,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,7 +1615,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5432</v>
+        <v>0.24576</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1630,7 +1624,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1640,25 +1634,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5270400000000001</v>
+        <v>0.234</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1662,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1677,7 +1671,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.49344</v>
+        <v>0.19304</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1690,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1705,7 +1699,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4192</v>
+        <v>0.15584</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1714,7 +1708,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1733,7 +1727,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3881600000000001</v>
+        <v>0.1358</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1742,7 +1736,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1761,7 +1755,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3856</v>
+        <v>0.13176</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1770,7 +1764,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1780,25 +1774,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.36</v>
+        <v>0.12336</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1808,25 +1802,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2992</v>
+        <v>0.1182</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1830,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1845,16 +1839,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.28832</v>
+        <v>0.1095</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1858,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1873,7 +1867,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.27632</v>
+        <v>0.1048</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1882,7 +1876,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1886,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.26784</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1910,7 +1904,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1929,7 +1923,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.25552</v>
+        <v>0.0964</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1938,7 +1932,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1948,25 +1942,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.2412</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -1976,25 +1970,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.234</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2004,7 +1998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2007,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.21664</v>
+        <v>0.06908</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2016,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2041,7 +2035,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.20224</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2050,7 +2044,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2060,25 +2054,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1182</v>
+        <v>0.06388000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2097,16 +2091,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.11776</v>
+        <v>0.06</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2116,25 +2110,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1095</v>
+        <v>0.06</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2144,25 +2138,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.104</v>
+        <v>0.06</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2166,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2181,7 +2175,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.09824000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2190,7 +2184,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2200,25 +2194,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.07600000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2228,25 +2222,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.06</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2256,16 +2250,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2274,7 +2268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2284,16 +2278,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.06</v>
+        <v>0.0474</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2302,7 +2296,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2306,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2321,16 +2315,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.05728</v>
+        <v>0.0468</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2340,16 +2334,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.054</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2358,7 +2352,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2368,16 +2362,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.048</v>
+        <v>0.0414</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2386,7 +2380,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2396,16 +2390,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.0474</v>
+        <v>0.0336</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2414,7 +2408,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2418,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2433,7 +2427,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.0474</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2442,7 +2436,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -2452,16 +2446,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.0456</v>
+        <v>0.0312</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2470,7 +2464,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2480,16 +2474,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0306</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2498,7 +2492,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2502,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2517,16 +2511,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0414</v>
+        <v>0.02944</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2536,25 +2530,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.03728</v>
+        <v>0.0294</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2564,16 +2558,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>power bi report</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0336</v>
+        <v>0.0288</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2592,25 +2586,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0336</v>
+        <v>0.026</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2620,16 +2614,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.0246</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2638,7 +2632,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2648,16 +2642,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.0312</v>
+        <v>0.0246</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2666,7 +2660,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2685,7 +2679,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.0304</v>
+        <v>0.02456</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2694,7 +2688,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2704,16 +2698,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0294</v>
+        <v>0.0228</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2722,7 +2716,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2732,16 +2726,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.0288</v>
+        <v>0.021</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2750,7 +2744,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2754,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2769,7 +2763,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0276</v>
+        <v>0.0198</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2778,7 +2772,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2782,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2797,7 +2791,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0246</v>
+        <v>0.0192</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2806,7 +2800,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2810,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2825,7 +2819,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0246</v>
+        <v>0.0192</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2834,7 +2828,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>data analytics software</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2853,16 +2847,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2866,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi free</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2881,7 +2875,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0234</v>
+        <v>0.0186</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2890,7 +2884,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2894,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data science and engineering</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2909,7 +2903,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0234</v>
+        <v>0.0186</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2918,7 +2912,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science+and+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2937,16 +2931,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.02304</v>
+        <v>0.0168</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -2956,16 +2950,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0228</v>
+        <v>0.0156</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2974,7 +2968,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2978,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2993,16 +2987,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.02224</v>
+        <v>0.015</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3006,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3021,7 +3015,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.021</v>
+        <v>0.0144</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3030,7 +3024,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3040,25 +3034,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.02016</v>
+        <v>0.0144</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3062,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3077,7 +3071,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0198</v>
+        <v>0.0144</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3086,7 +3080,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3090,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3105,16 +3099,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.01936</v>
+        <v>0.0144</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3118,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3133,16 +3127,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0192</v>
+        <v>0.01432</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3146,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3161,7 +3155,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0192</v>
+        <v>0.0132</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3170,7 +3164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3189,7 +3183,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0186</v>
+        <v>0.0132</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3198,7 +3192,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3202,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3217,7 +3211,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0186</v>
+        <v>0.0132</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3226,7 +3220,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3230,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3245,16 +3239,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.01808</v>
+        <v>0.0126</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3258,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3273,16 +3267,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.01792</v>
+        <v>0.0114</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3292,25 +3286,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.01744</v>
+        <v>0.0114</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi download desktop</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3329,7 +3323,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0168</v>
+        <v>0.0108</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3338,7 +3332,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3342,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3357,7 +3351,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0156</v>
+        <v>0.0102</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3366,7 +3360,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3376,16 +3370,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0156</v>
+        <v>0.0102</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3394,7 +3388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3398,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3413,16 +3407,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.01536</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3426,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3441,7 +3435,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.01536</v>
+        <v>0.00932</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3450,7 +3444,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3460,25 +3454,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0152</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3482,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3497,16 +3491,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.015</v>
+        <v>0.0076</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -3516,25 +3510,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.01472</v>
+        <v>0.0072</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3538,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3553,7 +3547,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0144</v>
+        <v>0.0072</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3562,7 +3556,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -3572,16 +3566,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.0144</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3594,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3609,16 +3603,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0144</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3622,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3637,7 +3631,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0132</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3646,7 +3640,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3650,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3665,7 +3659,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0132</v>
+        <v>0.006</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3674,7 +3668,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3678,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3693,16 +3687,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.01296</v>
+        <v>0.006</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3706,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3721,16 +3715,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.0126</v>
+        <v>0.00576</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3734,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3749,16 +3743,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.0114</v>
+        <v>0.00556</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3762,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>download power bi desktop</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3777,16 +3771,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0108</v>
+        <v>0.00504</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3790,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3805,7 +3799,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.0104</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3814,7 +3808,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3818,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3833,16 +3827,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.0102</v>
+        <v>0.00452</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3846,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3861,16 +3855,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0102</v>
+        <v>0.0045</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3874,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data analytics consulting</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3889,16 +3883,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0102</v>
+        <v>0.0045</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>data engineering tools</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3917,16 +3911,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.00448</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3930,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3945,16 +3939,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.00436</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>feature engineering</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3973,7 +3967,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3982,7 +3976,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=feature+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3986,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4001,7 +3995,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.00848</v>
+        <v>0.00384</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4010,7 +4004,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4014,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4029,7 +4023,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.00736</v>
+        <v>0.00384</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4038,7 +4032,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4048,25 +4042,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0072</v>
+        <v>0.0038</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4070,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4085,7 +4079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.0072</v>
+        <v>0.00368</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4104,16 +4098,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0036</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4122,7 +4116,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4126,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4141,7 +4135,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0064</v>
+        <v>0.0036</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4150,7 +4144,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4154,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4169,16 +4163,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.006</v>
+        <v>0.0036</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4182,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4197,16 +4191,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.006</v>
+        <v>0.00324</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4210,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4225,16 +4219,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.005920000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4238,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4253,16 +4247,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.00544</v>
+        <v>0.003</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4266,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>what is big data analytics</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4281,16 +4275,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.0026</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>masters in data analytics</t>
+          <t>data pipeline development</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4309,7 +4303,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.0024</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4318,7 +4312,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4322,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>coursera</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,16 +4331,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.00212</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=coursera</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4350,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4365,16 +4359,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0045</v>
+        <v>0.00184</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4384,25 +4378,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.0045</v>
+        <v>0.0018</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4406,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4421,7 +4415,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00432</v>
+        <v>0.0018</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4430,7 +4424,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4449,7 +4443,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.00384</v>
+        <v>0.0016</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4458,7 +4452,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4462,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4477,16 +4471,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.00368</v>
+        <v>0.0015</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4490,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4505,16 +4499,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0036</v>
+        <v>0.0015</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,16 +4527,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.003</v>
+        <v>0.00148</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4546,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4561,16 +4555,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.003</v>
+        <v>0.00136</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4574,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4589,16 +4583,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.00272</v>
+        <v>0.0012</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4602,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4617,16 +4611,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.00256</v>
+        <v>0.0012</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -4636,25 +4630,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.00256</v>
+        <v>0.0012</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4658,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4673,7 +4667,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0024</v>
+        <v>0.0012</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4682,7 +4676,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4692,16 +4686,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0018</v>
+        <v>0.0012</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4710,7 +4704,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4720,25 +4714,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4742,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4757,16 +4751,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4770,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4785,16 +4779,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.0012</v>
+        <v>0.00108</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4798,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>exmergo/dex</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4813,16 +4807,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0012</v>
+        <v>0.0009599999999999999</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/exmergo/dex</t>
         </is>
       </c>
     </row>
@@ -4832,25 +4826,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.0012</v>
+        <v>0.00092</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4854,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>Dreamerol/ALLSTATS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4869,16 +4863,100 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.0012</v>
+        <v>0.00068</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>etl data pipeline</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>trends</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A246"/>
+  <dimension ref="A1:A247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6138,481 +6216,488 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -457,12 +457,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.706</v>
+        <v>0.4482</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -625,25 +625,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5655</v>
+        <v>0.24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -681,16 +681,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -709,25 +709,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.31708</v>
+        <v>0.0486</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -803,25 +803,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>619941</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -829,7 +823,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -858,7 +852,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1133491</v>
+        <v>1133552</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -885,25 +879,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79875</v>
+        <v>619941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -911,7 +905,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -921,32 +915,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>mage-ai/mage-ai</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>16541265</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]" has 1199.6M views, but it's from 10 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>music</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16540035</v>
+        <v>1199563052</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.706</v>
+        <v>0.4482</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avoiding circular dependency errors in DAX</t>
+          <t>Cómo usar Power BI (Tutorial desde cero)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>41873</v>
+        <v>2873963</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1038,38 +1038,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1114</v>
+        <v>41873</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5655</v>
+        <v>0.24</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1079,26 +1079,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
+          <t>REVISIT — "Google Analytics in real life - online checkout" has 1.6M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
+          <t>Google Analytics in real life - online checkout</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7656832</v>
+        <v>1627722</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -1120,32 +1120,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data engineering</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>microsoft power bi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4635033</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -1160,33 +1166,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs" has 360.3M views, but it's from 7 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>John Cooper Clarke - Evidently Chickentown</t>
+          <t>Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2001417</v>
+        <v>360326670</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.31708</v>
+        <v>0.0486</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,7 +1304,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1316,7 +1322,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1326,16 +1332,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1344,7 +1350,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1354,25 +1360,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>what is a social engineering attack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.706</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
         </is>
       </c>
     </row>
@@ -1382,25 +1388,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5655</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1410,25 +1416,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5655</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1444,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>what is prompt engineering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.5442</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+prompt+engineering</t>
         </is>
       </c>
     </row>
@@ -1466,16 +1472,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>0.4482</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1484,7 +1490,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -1494,25 +1500,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.31708</v>
+        <v>0.36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1537,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1550,25 +1556,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>data analytics engineering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.278</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -1578,25 +1584,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.27504</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1612,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1615,7 +1621,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.24576</v>
+        <v>0.31712</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1624,7 +1630,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1640,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.234</v>
+        <v>0.278</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1668,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1671,7 +1677,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.19304</v>
+        <v>0.27504</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1680,7 +1686,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1696,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,7 +1705,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.15584</v>
+        <v>0.2458</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1708,7 +1714,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1718,25 +1724,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1358</v>
+        <v>0.24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1746,25 +1752,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.13176</v>
+        <v>0.234</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1780,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,7 +1789,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.12336</v>
+        <v>0.15584</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1792,7 +1798,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1802,25 +1808,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1182</v>
+        <v>0.1358</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1836,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1839,16 +1845,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1095</v>
+        <v>0.13176</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1858,25 +1864,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1048</v>
+        <v>0.1182</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1892,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1895,16 +1901,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.1095</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1920,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1923,7 +1929,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0964</v>
+        <v>0.1048</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1932,7 +1938,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1948,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1951,7 +1957,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1960,7 +1966,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1979,7 +1985,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1988,7 +1994,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2004,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,7 +2013,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.06908</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2016,7 +2022,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2032,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2035,7 +2041,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2044,7 +2050,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2054,25 +2060,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.06388000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2088,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2091,16 +2097,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2116,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2128,7 +2134,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2144,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>dashboard design ui</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2156,7 +2162,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2175,16 +2181,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.05416</v>
+        <v>0.06</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2194,16 +2200,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2212,7 +2218,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2231,7 +2237,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2240,7 +2246,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2256,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,7 +2265,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.048</v>
+        <v>0.05279999999999999</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2268,7 +2274,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2278,25 +2284,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.0474</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2312,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2315,7 +2321,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0468</v>
+        <v>0.0504</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2324,7 +2330,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2334,16 +2340,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0486</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2352,7 +2358,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2368,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2371,7 +2377,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0414</v>
+        <v>0.048</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2380,7 +2386,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2390,16 +2396,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.0336</v>
+        <v>0.0474</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2408,7 +2414,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2418,16 +2424,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2446,16 +2452,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.0312</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2464,7 +2470,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2474,16 +2480,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.0306</v>
+        <v>0.042</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2492,7 +2498,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2502,25 +2508,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.02944</v>
+        <v>0.0336</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2536,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2539,7 +2545,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0294</v>
+        <v>0.0312</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2548,7 +2554,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2564,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,7 +2573,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2576,7 +2582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2586,25 +2592,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.026</v>
+        <v>0.0306</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2614,16 +2620,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0246</v>
+        <v>0.0288</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2632,7 +2638,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2642,16 +2648,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.0246</v>
+        <v>0.0288</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2660,7 +2666,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2676,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2679,16 +2685,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.02456</v>
+        <v>0.024</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2698,16 +2704,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0228</v>
+        <v>0.024</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2716,7 +2722,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2732,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>ai dashboard design</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2735,7 +2741,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.021</v>
+        <v>0.0228</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2744,7 +2750,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2754,16 +2760,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0198</v>
+        <v>0.0222</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2772,7 +2778,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2797,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0192</v>
+        <v>0.0216</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2806,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2816,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2828,7 +2834,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2872,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2900,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2912,7 +2918,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2928,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,7 +2937,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0168</v>
+        <v>0.018</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2940,7 +2946,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2956,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2959,7 +2965,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0156</v>
+        <v>0.018</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2968,7 +2974,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2987,7 +2993,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.015</v>
+        <v>0.0168</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2996,7 +3002,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3015,7 +3021,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3024,7 +3030,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -3034,16 +3040,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3052,7 +3058,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3068,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3108,7 +3114,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3124,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3127,16 +3133,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.01432</v>
+        <v>0.0144</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,16 +3161,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0132</v>
+        <v>0.01432</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3180,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3183,7 +3189,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3192,7 +3198,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3202,16 +3208,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3220,7 +3226,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3239,7 +3245,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0126</v>
+        <v>0.0138</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3248,7 +3254,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3264,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3267,7 +3273,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0114</v>
+        <v>0.0132</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3276,7 +3282,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3286,16 +3292,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0114</v>
+        <v>0.0132</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3304,7 +3310,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>power bi download desktop</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3323,7 +3329,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0108</v>
+        <v>0.0132</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3332,7 +3338,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=travel</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3351,7 +3357,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0102</v>
+        <v>0.0126</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,7 +3366,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,7 +3385,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0102</v>
+        <v>0.0126</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3388,7 +3394,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>power bi web</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3407,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3416,7 +3422,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3432,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3435,16 +3441,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.00932</v>
+        <v>0.012</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3454,16 +3460,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>analytics dashboard design</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0114</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3472,7 +3478,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3488,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3491,16 +3497,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0076</v>
+        <v>0.0108</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=exercise</t>
         </is>
       </c>
     </row>
@@ -3510,16 +3516,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0072</v>
+        <v>0.0108</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3528,7 +3534,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3544,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>download power bi desktop</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3547,7 +3553,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0072</v>
+        <v>0.0108</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3556,7 +3562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3572,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3575,7 +3581,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3584,7 +3590,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3600,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3603,7 +3609,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3612,7 +3618,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3628,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>dashboard design template</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3631,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3640,7 +3646,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>curso power bi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3659,7 +3665,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.006</v>
+        <v>0.0102</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3668,7 +3674,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3684,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3687,16 +3693,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.006</v>
+        <v>0.0102</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3706,25 +3712,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.00576</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3740,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3743,16 +3749,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.00556</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3768,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3771,7 +3777,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.00504</v>
+        <v>0.00932</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3780,7 +3786,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3796,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3799,16 +3805,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3818,25 +3824,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.00452</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3852,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3855,16 +3861,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3880,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>excel dashboard design</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3883,16 +3889,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3908,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>dashboard design figma</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3911,16 +3917,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.00448</v>
+        <v>0.0078</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3936,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3939,7 +3945,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.00436</v>
+        <v>0.0076</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3948,7 +3954,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3964,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3967,7 +3973,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0042</v>
+        <v>0.0072</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3976,7 +3982,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -3986,25 +3992,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.00384</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4020,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4023,16 +4029,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.00384</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4048,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4051,16 +4057,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0038</v>
+        <v>0.006</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4076,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4079,16 +4085,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.00368</v>
+        <v>0.006</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4104,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4107,16 +4113,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.0036</v>
+        <v>0.00576</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4132,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4135,7 +4141,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0036</v>
+        <v>0.00556</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4144,7 +4150,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4160,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4163,16 +4169,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.0036</v>
+        <v>0.00504</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4188,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4191,7 +4197,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.00324</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4200,7 +4206,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4216,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4219,16 +4225,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4244,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4247,7 +4253,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4256,7 +4262,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4272,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4275,7 +4281,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.0026</v>
+        <v>0.00448</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4284,7 +4290,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4300,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4303,7 +4309,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0024</v>
+        <v>0.0042</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4312,7 +4318,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4328,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4331,7 +4337,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.00212</v>
+        <v>0.00384</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4340,7 +4346,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4356,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4359,7 +4365,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.00184</v>
+        <v>0.0038</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4368,7 +4374,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4378,25 +4384,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.0018</v>
+        <v>0.00368</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4406,25 +4412,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4443,16 +4449,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0016</v>
+        <v>0.0036</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4468,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4471,16 +4477,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.0015</v>
+        <v>0.0036</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4499,16 +4505,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4524,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>data engineering vs data analytics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4527,16 +4533,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.00148</v>
+        <v>0.003</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4552,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,16 +4561,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.00136</v>
+        <v>0.003</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4580,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4583,16 +4589,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0012</v>
+        <v>0.0026</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4608,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4611,16 +4617,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0012</v>
+        <v>0.00184</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4636,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4639,7 +4645,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4648,7 +4654,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4664,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,16 +4673,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4692,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,16 +4701,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0012</v>
+        <v>0.0016</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4714,25 +4720,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4748,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4751,16 +4757,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4776,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4779,7 +4785,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.00108</v>
+        <v>0.00148</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4788,7 +4794,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4804,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4807,16 +4813,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0009599999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4832,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4835,16 +4841,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.00092</v>
+        <v>0.0012</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4854,25 +4860,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.00068</v>
+        <v>0.0012</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4888,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4891,16 +4897,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4916,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4919,16 +4925,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4938,23 +4944,247 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>data pipeline meaning</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>etl pipeline</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=etl+pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>etl data pipeline</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
@@ -4971,7 +5201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A247"/>
+  <dimension ref="A1:A390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5173,1531 +5403,2532 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>balanced scorecard vs kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best ai agent analytics tools</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>best ai for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best ai tool for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best dashboard design home assistant</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best dashboard design in excel</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best dashboard design in power bi</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best dashboard design ui</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data analytics books</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best data analytics software</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>best data engineering books</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>best data pipeline</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>best free kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>best kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>best kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>best kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>best kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>best power bi books</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>best power bi certification</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>best power bi courses</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>best power bi dax book</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>best power bi dax course</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>best power bi training</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>better than chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>budget vs actual dashboard design</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>business intelligence trends</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>business intelligence trends 2024</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>business intelligence trends 2025</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>business intelligence trends 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>chatgpt for data analysis course</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>chatgpt for data analysis free</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>chatgpt for data analysis pdf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>chatgpt for data analysis udemy</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>claude ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>claude vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>claude vs chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>copilot vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>dashboard design</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>dashboard design ideas</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>dashboard design meaning</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>dashboard design rules</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>dashboard design skill</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>dashboard design skill claude code</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>dashboard design standards</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>dashboard design tips</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>data analytics</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>data analytics course</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>data analytics internship</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>data analytics jobs near me</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>data analytics vs data analysis</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>data engineering</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>data engineering academy</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>data pipeline station</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
+        <is>
+          <t>perplexity vs chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>power bi app</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>power bi certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>power bi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>power bi dax best practices</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>power bi dax cheat sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>power bi dax filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>power bi dax functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>power bi dax functions list</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>power bi dax if statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>power bi dax queries</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>power bi dax query view</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>power bi dax switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>power bi dax tutorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>power bi dax vs power query</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>power bi desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>power bi desktop download</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>power bi download</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>power bi login</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>power bi report builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>power bi training</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>power bi vs power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>software vs data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>stakeholder reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>stakeholder reporting forvis mazars</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>stakeholder reporting gmbh</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>stakeholder reporting hamburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>stakeholder reporting meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>stakeholder reporting template</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>statistics vs data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>tableau vs power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>top 10 power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>top 5 power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>top data pipeline solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>top kpi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>top n power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>top power bi dax functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>top power bi dax interview questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>types of dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>use of ai in analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>using chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>visual studio data pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>vs data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>vs power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>what is a floating element in tableau dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>what is a good dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>what is ai in analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>what is analytics engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>what is analytics engineering dbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>what is analytics engineering reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>what is bi dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>what is dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>what is data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>what is data analytics and visualization</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>what is data analytics degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>what is data analytics engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>what is data analytics in accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>what is data analytics in healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>what is data analytics in simple words</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>what is data analytics job</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>what is data analytics salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>what is data analytics used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>what is data analytics vs data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>what is data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>what is data engineering all about</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>what is data engineering and analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>what is data engineering and data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>what is data engineering course</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>what is data engineering in simple words</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>what is data engineering reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>what is data engineering role</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>what is data engineering salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>what is data engineering skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>what is data engineering vs data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>what is data pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>what is data pipeline architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>what is data pipeline development</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>what is data pipeline in ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>what is data pipeline in data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>what is data pipeline in data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>what is data pipeline in etl</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>what is data pipeline in machine learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>what is data pipeline in python</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>what is data pipeline in sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>what is data pipeline management</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>what is data pipeline orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>what is data pipeline testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard development</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard in excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard in power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard in tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>what is llm analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>what is power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>what is power bi and how does it work</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>what is power bi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>what is power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>what is power bi dax code</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>what is power bi dax function</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>what is power bi dax measures</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>what is power bi dax query</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>what is power bi dax studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>what is power bi dax used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>what is power bi desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>what is power bi pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>what is power bi report builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>what is power bi service</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>what is power bi software</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>what is power bi stand for</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>what is power bi used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>what is saas dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>what is stakeholder reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>what is the best chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>what is the best version of chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>what is the fundamental challenge of dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>what language is power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>why data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>why data analytics as a career</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>why data analytics course</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>why data analytics is a good career</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>why data analytics is important</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>why data analytics is the future</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>why data analytics is the future of everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>why data analytics is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>why data analytics reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>why data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>why data engineering interview questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>why data engineering is hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>why data engineering is important</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>why data engineering reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>why data pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>why power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>why power bi gateway went offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>why power bi is better than excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>why power bi is better than tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>why power bi is important</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>why power bi is not available for mac</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>why power bi is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>why power bi over excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4482</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=music</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -653,25 +653,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0672</v>
+        <v>0.19324</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>0.1234</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0486</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=jobs</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -798,21 +798,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data Engineering Course for Beginners</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1133570</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
@@ -823,7 +829,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -833,26 +839,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Engineering Course for Beginners</t>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1133552</v>
+        <v>79908</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -864,7 +870,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -879,25 +885,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>619941</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -915,26 +915,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16541265</v>
+        <v>619941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -942,11 +942,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVISIT — "Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]" has 1199.6M views, but it's from 10 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]</t>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1199563052</v>
+        <v>16541568</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4482</v>
+        <v>0.706</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=music</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2873963</v>
+        <v>2873994</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1079,38 +1079,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REVISIT — "Google Analytics in real life - online checkout" has 1.6M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("LangWatch LLM Optimization Studio", 89.1k views). Your angle: claim the space — straightforward, solid coverage of "langwatch/langwatch" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Google Analytics in real life - online checkout</t>
+          <t>LangWatch LLM Optimization Studio</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1627722</v>
+        <v>89121</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.0672</v>
+        <v>0.19324</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1120,38 +1120,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending", 1.2k views). Your angle: claim the space — straightforward, solid coverage of "spiceai/spiceai" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
+          <t>मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4635033</v>
+        <v>1215</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.06</v>
+        <v>0.1234</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1166,21 +1166,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs" has 360.3M views, but it's from 7 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs</t>
+          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>360326670</v>
+        <v>4635045</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.0486</v>
+        <v>0.06</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=jobs</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1332,16 +1332,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is a social engineering attack</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1388,25 +1388,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>what is a social engineering attack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5655</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
         </is>
       </c>
     </row>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.5655</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1444,25 +1444,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>what is prompt engineering</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5442</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+prompt+engineering</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1472,16 +1472,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4482</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=music</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1528,16 +1528,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>data analytics engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.36</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>data analytics engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3594000000000001</v>
+        <v>0.3171600000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.31712</v>
+        <v>0.278</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.278</v>
+        <v>0.27504</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.27504</v>
+        <v>0.2458</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1696,25 +1696,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2458</v>
+        <v>0.24</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.24</v>
+        <v>0.234</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.234</v>
+        <v>0.19324</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1864,25 +1864,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1182</v>
+        <v>0.1234</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1892,25 +1892,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1095</v>
+        <v>0.1182</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1048</v>
+        <v>0.1095</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.1048</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0964</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06908</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -2060,25 +2060,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.0672</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2116,25 +2116,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.06</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dashboard design ui</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.06</v>
+        <v>0.06392</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.05416</v>
+        <v>0.06</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2256,16 +2256,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>dashboard design ui</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.05279999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>best dashboard design</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0504</v>
+        <v>0.05279999999999999</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2340,25 +2340,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.0486</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=jobs</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.048</v>
+        <v>0.0504</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2396,16 +2396,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.0474</v>
+        <v>0.048</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0474</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.042</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2508,16 +2508,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0336</v>
+        <v>0.042</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0312</v>
+        <v>0.0336</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0306</v>
+        <v>0.0312</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2648,25 +2648,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.0288</v>
+        <v>0.02944</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2676,16 +2676,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.024</v>
+        <v>0.0288</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2704,16 +2704,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.024</v>
+        <v>0.0288</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ai dashboard design</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2741,16 +2741,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.0228</v>
+        <v>0.026</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2760,25 +2760,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0222</v>
+        <v>0.02456</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0216</v>
+        <v>0.024</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0192</v>
+        <v>0.024</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>ai dashboard design</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2853,16 +2853,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.019</v>
+        <v>0.0228</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2872,16 +2872,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0186</v>
+        <v>0.0222</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0186</v>
+        <v>0.0216</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2965,16 +2965,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0168</v>
+        <v>0.0186</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>business analytics</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0156</v>
+        <v>0.0186</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.0156</v>
+        <v>0.018</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0144</v>
+        <v>0.018</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.0144</v>
+        <v>0.0168</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.01432</v>
+        <v>0.0156</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>modern dashboard design</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3208,16 +3208,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0132</v>
+        <v>0.01432</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=travel</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3348,16 +3348,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0126</v>
+        <v>0.0138</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0126</v>
+        <v>0.0132</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.012</v>
+        <v>0.0132</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.012</v>
+        <v>0.0126</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>analytics dashboard design</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0108</v>
+        <v>0.012</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=exercise</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>bi dashboard design</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0108</v>
+        <v>0.012</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>download power bi desktop</t>
+          <t>analytics dashboard design</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>download power bi desktop</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>admin dashboard design</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3628,16 +3628,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>dashboard design template</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>curso power bi</t>
+          <t>dashboard design template</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3712,16 +3712,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>curso power bi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
+          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3777,16 +3777,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.00932</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>information dashboard design</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3805,16 +3805,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.00936</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>user dashboard design</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
+          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3880,16 +3880,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>excel dashboard design</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dashboard design figma</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0078</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>excel dashboard design</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3945,16 +3945,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0076</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>dashboard design figma</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0072</v>
+        <v>0.0078</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
         </is>
       </c>
     </row>
@@ -3992,25 +3992,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0076</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4048,25 +4048,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.006</v>
+        <v>0.0072</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.006</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -4104,25 +4104,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.00576</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.00556</v>
+        <v>0.006</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4169,16 +4169,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.00504</v>
+        <v>0.006</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.00576</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4225,16 +4225,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.0045</v>
+        <v>0.00556</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4253,16 +4253,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.0045</v>
+        <v>0.00504</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.00448</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0042</v>
+        <v>0.004560000000000001</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,16 +4337,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.00384</v>
+        <v>0.0045</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4365,16 +4365,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0038</v>
+        <v>0.0045</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.00368</v>
+        <v>0.00448</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4412,25 +4412,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.0036</v>
+        <v>0.00436</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0036</v>
+        <v>0.0042</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.0036</v>
+        <v>0.00384</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4505,16 +4505,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.003</v>
+        <v>0.00384</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>data engineering vs data analytics</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,16 +4533,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.003</v>
+        <v>0.0038</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4561,16 +4561,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.003</v>
+        <v>0.00368</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4589,16 +4589,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0026</v>
+        <v>0.0036</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4608,25 +4608,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.00184</v>
+        <v>0.0036</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4636,25 +4636,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0018</v>
+        <v>0.00324</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0016</v>
+        <v>0.003</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>data engineering vs data analytics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4757,16 +4757,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.00148</v>
+        <v>0.0026</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>data pipeline development</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0012</v>
+        <v>0.0024</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4841,16 +4841,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.0012</v>
+        <v>0.00212</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4860,25 +4860,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.0012</v>
+        <v>0.00184</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4888,16 +4888,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4925,16 +4925,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4944,25 +4944,25 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.0012</v>
+        <v>0.0016</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4981,16 +4981,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.00108</v>
+        <v>0.0015</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5009,16 +5009,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.0009599999999999999</v>
+        <v>0.0015</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.00092</v>
+        <v>0.00148</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.00068</v>
+        <v>0.00136</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5093,16 +5093,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5121,16 +5121,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>etl pipeline</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5168,23 +5168,275 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>data pipeline architecture</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>data pipeline meaning</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>data pipeline aws</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>etl data pipeline</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
@@ -5201,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A390"/>
+  <dimension ref="A1:A379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5221,2714 +5473,2637 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ai agent analytics</t>
+          <t>ai vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard</t>
+          <t>ai vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard servicenow</t>
+          <t>analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ai agent analytics platform</t>
+          <t>analytics engineering best practices</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ai agent analytics servicenow</t>
+          <t>analytics engineering course</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ai agent analytics vidhya</t>
+          <t>analytics engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ai in analytics</t>
+          <t>analytics engineering manager</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ai in analytics course</t>
+          <t>analytics engineering podcast</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ai vs data analytics</t>
+          <t>analytics engineering roundup</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ai vs data engineering</t>
+          <t>analytics engineering salary</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>analytics engineering</t>
+          <t>analytics engineering vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>analytics engineering best practices</t>
+          <t>analytics engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>analytics engineering course</t>
+          <t>analytics engineering with sql and dbt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>analytics engineering jobs</t>
+          <t>analytics engineering with sql and dbt pdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>analytics engineering manager</t>
+          <t>analytics vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>analytics engineering podcast</t>
+          <t>and data analytics</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>analytics engineering roundup</t>
+          <t>api vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>analytics engineering salary</t>
+          <t>backend vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>analytics engineering vs data engineering</t>
+          <t>balanced scorecard vs kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>analytics engineering vs data science</t>
+          <t>best ai for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt</t>
+          <t>best ai tool for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt pdf</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>analytics vs data engineering</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>and data analytics</t>
+          <t>best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>api vs data pipeline</t>
+          <t>best dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>backend vs data engineering</t>
+          <t>best dashboard design home assistant</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>balanced scorecard vs kpi dashboard</t>
+          <t>best dashboard design in excel</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>best dashboard design in power bi</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>best ai for power bi dax</t>
+          <t>best dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>best ai tool for power bi dax</t>
+          <t>best dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>best dashboard design ui</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best chatgpt for data analysis</t>
+          <t>best data analytics books</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best dashboard design examples</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best dashboard design home assistant</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>best dashboard design in excel</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>best dashboard design in power bi</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>best dashboard design inspiration</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>best dashboard design principles</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>best dashboard design templates</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best dashboard design ui</t>
+          <t>best data analytics software</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best data engineering books</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best data pipeline</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best free kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>best kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best power bi books</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best power bi certification</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best power bi courses</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>best free kpi dashboard software</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>best kpi dashboard design</t>
+          <t>best power bi dax book</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>best kpi dashboard excel</t>
+          <t>best power bi dax course</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>best kpi dashboard in power bi</t>
+          <t>best power bi training</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>best kpi dashboard software</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>better than chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>budget vs actual dashboard design</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>business intelligence trends</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>business intelligence trends 2024</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>best power bi dax book</t>
+          <t>business intelligence trends 2025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>best power bi dax course</t>
+          <t>business intelligence trends 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>chatgpt for data analysis course</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>better than chatgpt for data analysis</t>
+          <t>chatgpt for data analysis free</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>budget vs actual dashboard design</t>
+          <t>chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>business intelligence trends</t>
+          <t>chatgpt for data analysis pdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>business intelligence trends 2024</t>
+          <t>chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>business intelligence trends 2025</t>
+          <t>chatgpt for data analysis udemy</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>business intelligence trends 2026</t>
+          <t>claude ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>claude vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis</t>
+          <t>claude vs chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis course</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis free</t>
+          <t>copilot vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis in excel</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis pdf</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis reddit</t>
+          <t>dashboard design</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis udemy</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>claude ai vs chatgpt for data analysis</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis</t>
+          <t>dashboard design ideas</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis reddit</t>
+          <t>dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>dashboard design meaning</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>copilot vs chatgpt for data analysis</t>
+          <t>dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>dashboard design rules</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>dashboard design skill</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dashboard design</t>
+          <t>dashboard design skill claude code</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>dashboard design standards</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dashboard design ideas</t>
+          <t>dashboard design tips</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dashboard design inspiration</t>
+          <t>data analytics</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dashboard design meaning</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>dashboard design principles</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dashboard design rules</t>
+          <t>data analytics internships</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dashboard design skill</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dashboard design skill claude code</t>
+          <t>data analytics jobs entry level</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dashboard design standards</t>
+          <t>data analytics masters</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dashboard design templates</t>
+          <t>data analytics professional certificate</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dashboard design tips</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data engineering</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>data engineering academy</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>data analytics internship</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data engineering internship</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data analytics jobs near me</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data analytics meaning</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data analytics vs data analysis</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>data pipeline</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>data engineering certification</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data pipeline examples</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>data engineering salary</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>data engineering vs data science</t>
+          <t>data pipeline station</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>data pipeline engineer</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>data pipeline orchestration</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>data pipeline station</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>deepseek vs chatgpt for data analysis</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>gemini vs chatgpt for data analysis</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>good kpi dashboard</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>good vs bad dashboard design</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>grok vs chatgpt for data analysis</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>how good is chatgpt for data analysis</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>how reliable is chatgpt for data analysis</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>how to comment power bi dax</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>how to concatenate in power bi dax</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in excel from scratch</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in google sheets</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in excel</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in power bi</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in tableau</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>how to dashboard design</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>how to design kpi dashboard</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>how to divide in power bi dax</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>how to learn power bi dax</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>how to multiply in power bi dax</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>how to open power bi dax</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>how to power bi dax</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>how to practice power bi dax</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis in excel</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>how to use power bi dax</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>how to write power bi dax</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>if or power bi dax</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>julius ai vs chatgpt for data analysis</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>julius vs chatgpt for data analysis</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kpi dashboard</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kpi dashboard design</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kpi dashboard examples</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kpi dashboard excel</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kpi dashboard ideas</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kpi dashboard meaning</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kpi dashboard power bi</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kpi dashboard template</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kpi dashboard template excel</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>perplexity vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>llm for bi</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>power bi dax</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>power bi dax best practices</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>power bi dax cheat sheet</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>power bi dax filter</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>perplexity vs chatgpt for data analysis</t>
+          <t>power bi dax functions list</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi dax if</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>power bi app</t>
+          <t>power bi dax if statement</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi dax queries</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi dax query view</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>power bi dax</t>
+          <t>power bi dax switch</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>power bi dax best practices</t>
+          <t>power bi dax vs power query</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>power bi dax cheat sheet</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>power bi dax filter</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>power bi dax functions</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>power bi dax functions list</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>power bi dax if statement</t>
+          <t>power bi service</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>power bi dax queries</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>power bi dax query view</t>
+          <t>power bi vs power bi dax</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>power bi dax switch</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>power bi dax tutorial</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>power bi dax vs power query</t>
+          <t>stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>stakeholder reporting forvis mazars</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>stakeholder reporting gmbh</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>stakeholder reporting hamburg</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>power bi report builder</t>
+          <t>stakeholder reporting meaning</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>stakeholder reporting template</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>power bi vs power bi dax</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>stakeholder reporting</t>
+          <t>top 10 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>stakeholder reporting forvis mazars</t>
+          <t>top 5 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh &amp; co kg</t>
+          <t>top kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>stakeholder reporting hamburg</t>
+          <t>top n power bi dax</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>stakeholder reporting meaning</t>
+          <t>top power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>stakeholder reporting template</t>
+          <t>top power bi dax interview questions</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>types of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>using chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>top 10 power bi dax</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>top 5 power bi dax</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>top kpi dashboard</t>
+          <t>what is a floating element in tableau dashboard design</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>top n power bi dax</t>
+          <t>what is a good dashboard design</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>top power bi dax functions</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>top power bi dax interview questions</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>types of dashboard design</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>what is bi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>using chatgpt for data analysis</t>
+          <t>what is dashboard design</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>what is a floating element in tableau dashboard design</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>what is a good dashboard design</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>what is bi dashboard design</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>what is dashboard design</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is kpi dashboard development</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is power bi dax code</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>what is kpi dashboard</t>
+          <t>what is power bi dax function</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>what is kpi dashboard development</t>
+          <t>what is power bi dax measures</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in excel</t>
+          <t>what is power bi dax query</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in power bi</t>
+          <t>what is power bi dax studio</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in tableau</t>
+          <t>what is power bi dax used for</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>what is power bi dax</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>what is power bi dax code</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>what is power bi dax function</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>what is power bi dax measures</t>
+          <t>what is saas dashboard design</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>what is power bi dax query</t>
+          <t>what is stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>what is power bi dax studio</t>
+          <t>what is the best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>what is power bi dax used for</t>
+          <t>what is the best version of chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is the fundamental challenge of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what language is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>what is saas dashboard design</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>what is stakeholder reporting</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>what is the best chatgpt for data analysis</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>what is the best version of chatgpt for data analysis</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>what is the fundamental challenge of dashboard design</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>what language is power bi dax</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
-        <is>
-          <t>why data engineering reddit</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>why data pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>why power bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>why power bi gateway went offline</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>why power bi is better than excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>why power bi is better than tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>why power bi is important</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>why power bi is not available for mac</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>why power bi is used</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>why power bi over excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>why power bi over tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.36</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -625,16 +625,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1133570</v>
+        <v>1133623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16541568</v>
+        <v>16542114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cómo usar Power BI (Tutorial desde cero)</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2873994</v>
+        <v>41873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.36</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1043,33 +1043,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avoiding circular dependency errors in DAX</t>
+          <t>Cómo usar Power BI (Tutorial desde cero)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>41873</v>
+        <v>2874055</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending", 1.2k views). Your angle: claim the space — straightforward, solid coverage of "spiceai/spiceai" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "spiceai/spiceai" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1133,14 +1133,8 @@
           <t>spiceai/spiceai</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1215</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>NEW / SPIKE</t>
@@ -1166,25 +1160,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)" has 3.1M views, but it's from 4 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
+          <t>Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4635045</v>
+        <v>3058195</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1192,7 +1186,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,16 +1382,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>what is a social engineering attack</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1406,7 +1400,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1494,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1509,16 +1503,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.36</v>
+        <v>0.3171600000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1528,16 +1522,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>data analytics engineering</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3594000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1546,7 +1540,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1556,25 +1550,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.3594000000000001</v>
+        <v>0.278</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1578,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1593,7 +1587,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3171600000000001</v>
+        <v>0.27504</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1602,7 +1596,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1606,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,7 +1615,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.278</v>
+        <v>0.2458</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1630,7 +1624,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1649,16 +1643,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.27504</v>
+        <v>0.2412</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -1668,25 +1662,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2458</v>
+        <v>0.234</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1696,25 +1690,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.24</v>
+        <v>0.19324</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1724,25 +1718,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.234</v>
+        <v>0.15584</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1761,7 +1755,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.19324</v>
+        <v>0.1358</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1770,7 +1764,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1774,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1789,7 +1783,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.15584</v>
+        <v>0.13176</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1798,7 +1792,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1802,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1817,7 +1811,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1358</v>
+        <v>0.1234</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1826,7 +1820,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1836,25 +1830,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.13176</v>
+        <v>0.1164</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1858,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1873,16 +1867,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1234</v>
+        <v>0.1125</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1892,25 +1886,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1182</v>
+        <v>0.1048</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1929,16 +1923,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1095</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1957,7 +1951,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1048</v>
+        <v>0.0964</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1966,7 +1960,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1970,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1985,7 +1979,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1994,7 +1988,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -2004,7 +1998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2007,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.0964</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2016,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2041,7 +2035,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2050,7 +2044,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2054,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2069,7 +2063,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2078,7 +2072,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2097,7 +2091,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06908</v>
+        <v>0.06392</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2106,7 +2100,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2125,16 +2119,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2138,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2153,16 +2147,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.06392</v>
+        <v>0.06</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2166,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2190,7 +2184,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2194,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>dax in power bi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2218,7 +2212,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=dax+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2222,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2246,7 +2240,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2250,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dashboard design ui</t>
+          <t>ui dashboard design</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2274,7 +2268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
+          <t>https://trends.google.com/trends/explore?q=ui+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2278,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>ui design</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2293,16 +2287,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.05416</v>
+        <v>0.0588</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=ui+design</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2306,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>dashboard ui</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.05279999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2330,7 +2324,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+ui</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2334,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2349,7 +2343,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2358,7 +2352,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2368,16 +2362,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>best dashboard design</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0504</v>
+        <v>0.0522</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2386,7 +2380,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2390,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2405,7 +2399,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2414,7 +2408,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2424,25 +2418,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.0474</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2455,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2480,16 +2474,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0474</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2498,7 +2492,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2502,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2517,7 +2511,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.042</v>
+        <v>0.0474</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2526,7 +2520,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2536,16 +2530,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0336</v>
+        <v>0.0444</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2554,7 +2548,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2564,16 +2558,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0312</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2592,16 +2586,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0306</v>
+        <v>0.0372</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2610,7 +2604,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2614,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2629,7 +2623,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0306</v>
+        <v>0.033</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2638,7 +2632,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2648,25 +2642,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.02944</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2685,7 +2679,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2694,7 +2688,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2704,16 +2698,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2722,7 +2716,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2732,25 +2726,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2760,25 +2754,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.02456</v>
+        <v>0.03</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2782,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2797,16 +2791,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.024</v>
+        <v>0.02944</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2810,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2825,16 +2819,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ai dashboard design</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2853,7 +2847,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.0228</v>
+        <v>0.0258</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2862,7 +2856,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2872,25 +2866,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0222</v>
+        <v>0.02456</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2894,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2909,7 +2903,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0216</v>
+        <v>0.024</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2918,7 +2912,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>ai dashboard design</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2937,7 +2931,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0192</v>
+        <v>0.0228</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2946,7 +2940,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2956,25 +2950,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.019</v>
+        <v>0.0228</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2978,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2993,7 +2987,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0186</v>
+        <v>0.0216</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3002,7 +2996,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3015,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0186</v>
+        <v>0.0192</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3040,7 +3034,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3049,7 +3043,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3058,7 +3052,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3062,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3077,7 +3071,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3086,7 +3080,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3090,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3105,16 +3099,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.0168</v>
+        <v>0.019</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3118,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>business analytics</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3133,7 +3127,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0156</v>
+        <v>0.0186</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3142,7 +3136,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3146,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3161,7 +3155,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0156</v>
+        <v>0.0168</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3170,7 +3164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3189,7 +3183,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0144</v>
+        <v>0.0162</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3198,7 +3192,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3208,16 +3202,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0144</v>
+        <v>0.015</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3226,7 +3220,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3230,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3245,7 +3239,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0144</v>
+        <v>0.015</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3254,7 +3248,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3258,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3273,16 +3267,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.01432</v>
+        <v>0.0144</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3286,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>modern dashboard design</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3301,7 +3295,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3310,7 +3304,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3329,7 +3323,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3338,7 +3332,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3348,25 +3342,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0138</v>
+        <v>0.01432</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3370,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3385,7 +3379,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3394,7 +3388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3398,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3422,7 +3416,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3426,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3441,7 +3435,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.0126</v>
+        <v>0.0132</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3450,7 +3444,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3463,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0126</v>
+        <v>0.0132</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3488,7 +3482,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3497,7 +3491,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.012</v>
+        <v>0.0126</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3506,7 +3500,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3538,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>analytics dashboard design</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3562,7 +3556,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3566,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>download power bi desktop</t>
+          <t>analytics dashboard design</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3581,7 +3575,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3600,16 +3594,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>bi dashboard design</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3618,7 +3612,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3622,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3646,7 +3640,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3650,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dashboard design template</t>
+          <t>power bi download desktop</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3665,7 +3659,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3674,7 +3668,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3678,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>admin dashboard design</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3693,7 +3687,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3702,7 +3696,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3706,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>admin dashboard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3730,7 +3724,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3734,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>curso power bi</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3758,7 +3752,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3762,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3777,7 +3771,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3786,7 +3780,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3790,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3805,16 +3799,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.00936</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -3824,16 +3818,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>information dashboard design</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3842,7 +3836,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3846,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user dashboard design</t>
+          <t>dashboard design template</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3861,7 +3855,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3870,7 +3864,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
         </is>
       </c>
     </row>
@@ -3880,16 +3874,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>dashboard template</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3898,7 +3892,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+template</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3917,16 +3911,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3930,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>excel dashboard design</t>
+          <t>user dashboard design</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3954,7 +3948,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>dashboard design figma</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3973,7 +3967,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0078</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3982,7 +3976,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3986,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>excel dashboard design</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4001,16 +3995,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0076</v>
+        <v>0.0078</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4014,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4029,7 +4023,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0072</v>
+        <v>0.0078</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4038,7 +4032,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -4048,25 +4042,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0072</v>
+        <v>0.0076</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -4076,16 +4070,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4104,16 +4098,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dax query in power bi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4122,7 +4116,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dax+query+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4126,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4141,16 +4135,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.006</v>
+        <v>0.0072</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4160,16 +4154,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.006</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4178,7 +4172,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4182,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4197,16 +4191,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.00576</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -4216,25 +4210,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.00556</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4238,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4253,16 +4247,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.00504</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4266,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4281,16 +4275,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4309,7 +4303,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.004560000000000001</v>
+        <v>0.00576</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4318,7 +4312,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4322,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,16 +4331,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.0045</v>
+        <v>0.00556</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4350,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>dax functions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4365,16 +4359,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0045</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=dax+functions</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4378,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>dax function in power bi</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4393,16 +4387,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.00448</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=dax+function+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4406,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4421,7 +4415,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00436</v>
+        <v>0.00504</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4430,7 +4424,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4449,16 +4443,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0042</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4462,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4477,7 +4471,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.00384</v>
+        <v>0.004560000000000001</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4486,7 +4480,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4490,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4505,16 +4499,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.00384</v>
+        <v>0.0045</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,16 +4527,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.0038</v>
+        <v>0.0045</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4546,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4561,7 +4555,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.00368</v>
+        <v>0.00448</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4570,7 +4564,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4574,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4589,16 +4583,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0036</v>
+        <v>0.00436</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -4608,16 +4602,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0036</v>
+        <v>0.0042</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4626,7 +4620,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4630,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4645,7 +4639,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0036</v>
+        <v>0.00384</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4654,7 +4648,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4658,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4673,7 +4667,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.00324</v>
+        <v>0.00384</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4682,7 +4676,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4686,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4701,16 +4695,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.003</v>
+        <v>0.0038</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4714,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4729,16 +4723,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.003</v>
+        <v>0.00368</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4742,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data engineering vs data analytics</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4757,16 +4751,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.003</v>
+        <v>0.00364</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4770,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>dax functions in power bi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4785,16 +4779,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.0026</v>
+        <v>0.0036</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=dax+functions+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4798,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4813,7 +4807,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0024</v>
+        <v>0.0036</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4822,7 +4816,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4826,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4841,16 +4835,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.00212</v>
+        <v>0.0036</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4854,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4869,7 +4863,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.00184</v>
+        <v>0.00324</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4878,7 +4872,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4888,25 +4882,25 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.0018</v>
+        <v>0.003</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4910,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4925,16 +4919,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.0018</v>
+        <v>0.003</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4938,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4953,7 +4947,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.0016</v>
+        <v>0.0026</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4962,7 +4956,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4966,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4981,16 +4975,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.0015</v>
+        <v>0.00212</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -5000,7 +4994,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5009,16 +5003,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.0015</v>
+        <v>0.00184</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -5028,25 +5022,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.00148</v>
+        <v>0.0018</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5050,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5065,7 +5059,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.00136</v>
+        <v>0.0018</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5074,7 +5068,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5078,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5093,16 +5087,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.0012</v>
+        <v>0.0016</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5106,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5121,16 +5115,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5134,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5149,16 +5143,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -5168,25 +5162,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.0012</v>
+        <v>0.00148</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5196,25 +5190,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.0012</v>
+        <v>0.00136</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5218,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5242,7 +5236,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5252,25 +5246,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.00108</v>
+        <v>0.0012</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5274,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5289,16 +5283,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.0009599999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5302,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5317,16 +5311,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.00092</v>
+        <v>0.0012</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5330,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5345,16 +5339,16 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.00068</v>
+        <v>0.0012</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -5364,25 +5358,25 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5386,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5401,7 +5395,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.00108</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5410,7 +5404,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -5420,23 +5414,163 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>etl data pipeline</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
@@ -5453,7 +5587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A379"/>
+  <dimension ref="A1:A377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5641,686 +5775,686 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>best dashboard design examples</t>
+          <t>best dashboard design</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>best dashboard design home assistant</t>
+          <t>best dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>best dashboard design in excel</t>
+          <t>best dashboard design home assistant</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>best dashboard design in power bi</t>
+          <t>best dashboard design in excel</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>best dashboard design inspiration</t>
+          <t>best dashboard design in power bi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>best dashboard design principles</t>
+          <t>best dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>best dashboard design templates</t>
+          <t>best dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>best dashboard design ui</t>
+          <t>best dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best dashboard design ui</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best data analytics books</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best data analytics software</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data engineering books</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best data pipeline</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best free kpi dashboard software</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>best kpi dashboard design</t>
+          <t>best free kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>best kpi dashboard excel</t>
+          <t>best kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>best kpi dashboard in power bi</t>
+          <t>best kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>best kpi dashboard software</t>
+          <t>best kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best power bi books</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>best power bi certification</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>best power bi courses</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>best power bi dax book</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>best power bi dax course</t>
+          <t>best power bi dax book</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>best power bi dax course</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>best power bi training</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>better than chatgpt for data analysis</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>budget vs actual dashboard design</t>
+          <t>better than chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>business intelligence trends</t>
+          <t>budget vs actual dashboard design</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>business intelligence trends 2024</t>
+          <t>business intelligence trends</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>business intelligence trends 2025</t>
+          <t>business intelligence trends 2024</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>business intelligence trends 2026</t>
+          <t>business intelligence trends 2025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>business intelligence trends 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis course</t>
+          <t>chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis free</t>
+          <t>chatgpt for data analysis course</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis in excel</t>
+          <t>chatgpt for data analysis free</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis pdf</t>
+          <t>chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis reddit</t>
+          <t>chatgpt for data analysis pdf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis udemy</t>
+          <t>chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>claude ai vs chatgpt for data analysis</t>
+          <t>chatgpt for data analysis udemy</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis</t>
+          <t>claude ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis reddit</t>
+          <t>claude vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>claude vs chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>copilot vs chatgpt for data analysis</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>copilot vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dashboard design</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>dashboard design</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dashboard design ideas</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dashboard design inspiration</t>
+          <t>dashboard design ideas</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dashboard design meaning</t>
+          <t>dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dashboard design principles</t>
+          <t>dashboard design meaning</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dashboard design rules</t>
+          <t>dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dashboard design skill</t>
+          <t>dashboard design rules</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dashboard design skill claude code</t>
+          <t>dashboard design skill</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dashboard design standards</t>
+          <t>dashboard design skill claude code</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dashboard design templates</t>
+          <t>dashboard design standards</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dashboard design tips</t>
+          <t>dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>dashboard design tips</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data analytics</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>data analytics jobs entry level</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>data analytics google certification</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>data analytics professional certificate</t>
+          <t>data analytics internships</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>data engineering</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>data engineering certification</t>
+          <t>data engineering academy</t>
         </is>
       </c>
     </row>
@@ -6334,56 +6468,56 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data engineering internship</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering manager</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data engineering reddit</t>
+          <t>data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data engineering salary</t>
+          <t>data engineering system design</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering things</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data engineering vs data science</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>data pipeline</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
     </row>
@@ -6397,1713 +6531,1699 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data pipeline architecture diagram</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>data pipeline engineer</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data pipeline examples</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>data pipeline orchestration</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>data pipeline station</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>deepseek vs chatgpt for data analysis</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>gemini vs chatgpt for data analysis</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>good kpi dashboard</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>good vs bad dashboard design</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>grok vs chatgpt for data analysis</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>how good is chatgpt for data analysis</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>how reliable is chatgpt for data analysis</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>how to comment power bi dax</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>how to concatenate in power bi dax</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in excel from scratch</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in google sheets</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in excel</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in power bi</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in tableau</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>how to dashboard design</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>how to design kpi dashboard</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>how to divide in power bi dax</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>how to learn power bi dax</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>how to multiply in power bi dax</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>how to open power bi dax</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>how to power bi dax</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>how to practice power bi dax</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis in excel</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>how to use power bi dax</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>how to write power bi dax</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>if or power bi dax</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>julius ai vs chatgpt for data analysis</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>julius vs chatgpt for data analysis</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kpi dashboard</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kpi dashboard design</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kpi dashboard examples</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kpi dashboard excel</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kpi dashboard ideas</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kpi dashboard meaning</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kpi dashboard power bi</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kpi dashboard template</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kpi dashboard template excel</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>llm for bi</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>perplexity vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>perplexity vs chatgpt for data analysis</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi courses</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi dax</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>power bi dax</t>
+          <t>power bi dax best practices</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>power bi dax best practices</t>
+          <t>power bi dax cheat sheet</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>power bi dax cheat sheet</t>
+          <t>power bi dax filter</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>power bi dax filter</t>
+          <t>power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>power bi dax functions</t>
+          <t>power bi dax functions list</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>power bi dax functions list</t>
+          <t>power bi dax if statement</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>power bi dax if</t>
+          <t>power bi dax queries</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>power bi dax if statement</t>
+          <t>power bi dax query view</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>power bi dax queries</t>
+          <t>power bi dax switch</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>power bi dax query view</t>
+          <t>power bi dax tutorial</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>power bi dax switch</t>
+          <t>power bi dax vs power query</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>power bi dax vs power query</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>power bi vs power bi dax</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>power bi vs power bi dax</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>stakeholder reporting forvis mazars</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>stakeholder reporting</t>
+          <t>stakeholder reporting gmbh</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>stakeholder reporting forvis mazars</t>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh</t>
+          <t>stakeholder reporting hamburg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh &amp; co kg</t>
+          <t>stakeholder reporting meaning</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>stakeholder reporting hamburg</t>
+          <t>stakeholder reporting template</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>stakeholder reporting meaning</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>stakeholder reporting template</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>top 10 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>top 5 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>top 10 power bi dax</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>top 5 power bi dax</t>
+          <t>top kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>top n power bi dax</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>top kpi dashboard</t>
+          <t>top power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>top n power bi dax</t>
+          <t>top power bi dax interview questions</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>top power bi dax functions</t>
+          <t>types of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>top power bi dax interview questions</t>
+          <t>using chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>types of dashboard design</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>using chatgpt for data analysis</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>what is a floating element in tableau dashboard design</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>what is a good dashboard design</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>what is a floating element in tableau dashboard design</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>what is a good dashboard design</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is bi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is dashboard design</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>what is bi dashboard design</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>what is dashboard design</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is kpi dashboard development</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>what is kpi dashboard</t>
+          <t>what is kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>what is kpi dashboard development</t>
+          <t>what is kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in excel</t>
+          <t>what is kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in tableau</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi dax code</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>what is power bi dax</t>
+          <t>what is power bi dax function</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>what is power bi dax code</t>
+          <t>what is power bi dax measures</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>what is power bi dax function</t>
+          <t>what is power bi dax query</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>what is power bi dax measures</t>
+          <t>what is power bi dax studio</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>what is power bi dax query</t>
+          <t>what is power bi dax used for</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>what is power bi dax studio</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>what is power bi dax used for</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is saas dashboard design</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>what is saas dashboard design</t>
+          <t>what is the best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>what is stakeholder reporting</t>
+          <t>what is the best version of chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>what is the best chatgpt for data analysis</t>
+          <t>what is the fundamental challenge of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>what is the best version of chatgpt for data analysis</t>
+          <t>what language is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>what is the fundamental challenge of dashboard design</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>what language is power bi dax</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
-        <is>
-          <t>why power bi over excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>why power bi over tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/reports/report_2026-09-19.xlsx
+++ b/reports/report_2026-09-19.xlsx
@@ -709,12 +709,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,25 +768,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Possibly Off-Niche</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Top Competing Video</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -803,7 +808,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago (2024) and likely outdated. Structure: a direct "what's changed since 2024" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -811,23 +816,26 @@
           <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1133623</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>1133651</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.8</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
@@ -844,7 +852,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — "langfuse/langfuse" has little to no video coverage yet (only one relevant video exists: "Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,23 +860,26 @@
           <t>langfuse/langfuse</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>79908</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://github.com/langfuse/langfuse</t>
         </is>
@@ -885,7 +896,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — "coreyhaines31/marketingskills" has little to no video coverage yet. Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -893,17 +904,20 @@
           <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.8</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
@@ -920,7 +934,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — "airbytehq/airbyte" has little to no video coverage yet (only one relevant video exists: "Airbyte 2.0: Enterprise Flex", 619.9k views). Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -928,23 +942,26 @@
           <t>airbytehq/airbyte</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>619941</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.8</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>https://github.com/airbytehq/airbyte</t>
         </is>
@@ -961,7 +978,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago (2021) and likely outdated. Structure: a direct "what's changed since 2021" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -969,23 +986,26 @@
           <t>mage-ai/mage-ai</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>16542114</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>16542417</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.706</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://github.com/mage-ai/mage-ai</t>
         </is>
@@ -1002,7 +1022,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago (2021) and likely outdated. Structure: a direct "what's changed since 2021" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1010,23 +1030,26 @@
           <t>circular dependency detected power bi</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>41873</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
@@ -1043,7 +1066,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago (2020) and likely outdated. Structure: a direct "what's changed since 2020" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1051,23 +1074,26 @@
           <t>power bi para que sirve</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Cómo usar Power BI (Tutorial desde cero)</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>2874055</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
+      <c r="G8" t="n">
+        <v>2874087</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.3</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
@@ -1084,7 +1110,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("LangWatch LLM Optimization Studio", 89.1k views). Your angle: claim the space — straightforward, solid coverage of "langwatch/langwatch" has almost no competition right now.</t>
+          <t>WHITESPACE — "langwatch/langwatch" has little to no video coverage yet (only one relevant video exists: "LangWatch LLM Optimization Studio", 89.1k views). Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,23 +1118,26 @@
           <t>langwatch/langwatch</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>LangWatch LLM Optimization Studio</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>89121</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.19324</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>https://github.com/langwatch/langwatch</t>
         </is>
@@ -1125,7 +1154,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "spiceai/spiceai" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — "spiceai/spiceai" has little to no video coverage yet. Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1133,17 +1162,20 @@
           <t>spiceai/spiceai</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.1234</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>https://github.com/spiceai/spiceai</t>
         </is>
@@ -1160,33 +1192,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)" has 3.1M views, but it's from 4 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Power BI Tutorial From Beginner to Pro ⚡ Desktop to Dashboard in 60 Minutes ⏰" has 5.8M views, but it's from 7 years ago (2019) and likely outdated. Structure: a direct "what's changed since 2019" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>3058195</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+          <t>power bi microsoft</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Power BI Tutorial From Beginner to Pro ⚡ Desktop to Dashboard in 60 Minutes ⏰</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5832760</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>EVERGREEN</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.06</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1669,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2412</v>
+        <v>0.234</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1697,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.234</v>
+        <v>0.19324</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1725,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,7 +1734,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.19324</v>
+        <v>0.15584</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1708,7 +1743,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1753,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1727,7 +1762,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.15584</v>
+        <v>0.1358</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1736,7 +1771,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1755,7 +1790,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1358</v>
+        <v>0.13176</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1764,7 +1799,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1809,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,7 +1818,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.13176</v>
+        <v>0.1234</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1792,7 +1827,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1802,25 +1837,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1234</v>
+        <v>0.1164</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1830,25 +1865,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1164</v>
+        <v>0.114</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1893,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1867,16 +1902,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1125</v>
+        <v>0.1048</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1921,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1895,7 +1930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1048</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1904,7 +1939,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1949,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1923,7 +1958,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.0964</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1932,7 +1967,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1977,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1951,7 +1986,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0964</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1960,7 +1995,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -1970,7 +2005,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1979,7 +2014,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1988,7 +2023,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2033,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,7 +2042,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2016,7 +2051,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2061,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2035,7 +2070,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06908</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2044,7 +2079,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2089,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2063,7 +2098,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06392</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2072,7 +2107,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2082,25 +2117,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06392</v>
+        <v>0.06</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2145,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2128,7 +2163,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2201,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>dax in power bi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2184,7 +2219,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=dax+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2229,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dax in power bi</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2212,7 +2247,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+in+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2257,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>ui dashboard design</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2240,7 +2275,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=ui+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2285,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ui dashboard design</t>
+          <t>dashboard ui</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,7 +2294,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.06</v>
+        <v>0.0588</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2268,7 +2303,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ui+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+ui</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2341,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dashboard ui</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2315,16 +2350,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0588</v>
+        <v>0.05416</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+ui</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2334,25 +2369,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.05416</v>
+        <v>0.0522</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2362,16 +2397,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0522</v>
+        <v>0.051</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2380,7 +2415,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2425,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>best dashboard design</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2399,16 +2434,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.051</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2418,25 +2453,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2481,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2455,7 +2490,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.048</v>
+        <v>0.0474</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2464,7 +2499,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2509,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2492,7 +2527,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2537,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2511,7 +2546,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0474</v>
+        <v>0.045</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2520,7 +2555,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2565,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2539,7 +2574,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0444</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2548,7 +2583,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2593,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,7 +2602,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2576,7 +2611,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2586,16 +2621,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0372</v>
+        <v>0.033</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2604,7 +2639,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2649,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2623,7 +2658,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.033</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2632,7 +2667,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2677,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2651,7 +2686,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.0306</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2660,7 +2695,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2705,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2688,7 +2723,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2698,16 +2733,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0306</v>
+        <v>0.03</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2716,7 +2751,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2754,25 +2789,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.03</v>
+        <v>0.02944</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2817,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2826,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.02944</v>
+        <v>0.026</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2835,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2845,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2819,16 +2854,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.026</v>
+        <v>0.0258</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2873,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,16 +2882,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.0258</v>
+        <v>0.02456</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2901,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2875,16 +2910,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.02456</v>
+        <v>0.024</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2929,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.024</v>
+        <v>0.0228</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2912,7 +2947,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2950,16 +2985,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0228</v>
+        <v>0.0216</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2968,7 +3003,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3013,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2987,7 +3022,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0216</v>
+        <v>0.0192</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2996,7 +3031,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3071,16 +3106,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0192</v>
+        <v>0.019</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3125,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3099,16 +3134,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.019</v>
+        <v>0.0186</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3153,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3127,7 +3162,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0186</v>
+        <v>0.0168</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3136,7 +3171,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3181,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,7 +3190,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0168</v>
+        <v>0.0162</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3164,7 +3199,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3209,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3183,7 +3218,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0162</v>
+        <v>0.015</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3192,7 +3227,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3265,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3239,7 +3274,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.015</v>
+        <v>0.0144</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3248,7 +3283,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3293,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3276,7 +3311,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3321,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3304,7 +3339,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3349,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3323,16 +3358,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0144</v>
+        <v>0.01432</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3377,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3351,16 +3386,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.01432</v>
+        <v>0.0138</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3405,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>modern dashboard design</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,7 +3414,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0138</v>
+        <v>0.0132</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3388,7 +3423,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3461,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3444,7 +3479,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3489,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3463,7 +3498,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0132</v>
+        <v>0.0126</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3472,7 +3507,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3517,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3491,7 +3526,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0126</v>
+        <v>0.012</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3500,7 +3535,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3545,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3519,7 +3554,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.012</v>
+        <v>0.0114</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3528,7 +3563,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3573,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3556,7 +3591,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3594,16 +3629,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0114</v>
+        <v>0.0108</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3612,7 +3647,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3713,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>bi dashboard design</t>
+          <t>admin dashboard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3687,7 +3722,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3696,7 +3731,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3741,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>admin dashboard</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3724,7 +3759,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3769,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3752,7 +3787,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3797,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>admin dashboard design</t>
+          <t>dashboard template</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3771,7 +3806,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0102</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3780,7 +3815,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+template</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3909,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>dashboard template</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3883,16 +3918,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+template</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3937,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3911,16 +3946,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0094</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3965,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user dashboard design</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3948,7 +3983,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3993,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>information dashboard design</t>
+          <t>user dashboard design</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3976,7 +4011,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4049,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4023,16 +4058,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0078</v>
+        <v>0.0076</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4077,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4051,16 +4086,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0076</v>
+        <v>0.0072</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4105,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>dax query in power bi</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4088,7 +4123,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dax+query+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4133,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>dax query in power bi</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4116,7 +4151,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+query+in+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4126,16 +4161,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0072</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4144,7 +4179,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4189,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4172,7 +4207,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4273,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4247,16 +4282,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4301,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4275,16 +4310,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.006</v>
+        <v>0.00576</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4329,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4303,7 +4338,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.00576</v>
+        <v>0.00556</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4312,7 +4347,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4357,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>dax function in power bi</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4331,16 +4366,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.00556</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dax+function+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4413,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>dax function in power bi</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4387,16 +4422,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.00504</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+function+in+power+bi</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4441,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4415,7 +4450,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00504</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4424,7 +4459,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4469,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4443,7 +4478,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.004560000000000001</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4452,7 +4487,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4497,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4471,16 +4506,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.004560000000000001</v>
+        <v>0.0045</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4525,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4508,7 +4543,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4553,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4527,16 +4562,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.0045</v>
+        <v>0.00448</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4581,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,7 +4590,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.00448</v>
+        <v>0.00436</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4564,7 +4599,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4609,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4583,16 +4618,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.00436</v>
+        <v>0.0042</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4637,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4611,16 +4646,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0042</v>
+        <v>0.00384</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4693,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,7 +4702,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.00384</v>
+        <v>0.0038</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4676,7 +4711,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4721,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,7 +4730,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0038</v>
+        <v>0.00368</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4704,7 +4739,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4749,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4723,7 +4758,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.00368</v>
+        <v>0.00364</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4732,7 +4767,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4777,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4751,16 +4786,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.00364</v>
+        <v>0.0036</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4805,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>dax functions in power bi</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4788,7 +4823,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+functions+in+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4833,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4807,16 +4842,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0036</v>
+        <v>0.00324</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4861,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4835,16 +4870,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.0036</v>
+        <v>0.003</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4889,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4863,16 +4898,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.00324</v>
+        <v>0.003</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4917,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4891,16 +4926,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4945,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4919,7 +4954,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.003</v>
+        <v>0.0024</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4928,7 +4963,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4973,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4947,7 +4982,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.0026</v>
+        <v>0.00212</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4956,7 +4991,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5001,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4975,7 +5010,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.00212</v>
+        <v>0.00184</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4984,7 +5019,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4994,25 +5029,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.00184</v>
+        <v>0.0018</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -5022,12 +5057,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5035,12 +5070,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5085,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5059,7 +5094,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.0018</v>
+        <v>0.0016</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5068,7 +5103,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5113,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5087,16 +5122,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5169,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5143,16 +5178,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.0015</v>
+        <v>0.00148</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5197,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5171,7 +5206,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.00148</v>
+        <v>0.00136</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5180,7 +5215,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5225,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5199,16 +5234,16 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.00136</v>
+        <v>0.0012</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5253,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5236,7 +5271,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5281,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5264,7 +5299,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5309,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5292,7 +5327,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5337,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5320,7 +5355,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A377"/>
+  <dimension ref="A1:A378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6412,35 +6447,35 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>data analytics internship</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics jobs remote</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
@@ -6461,56 +6496,56 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6566,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>data pipeline design</t>
         </is>
       </c>
     </row>
@@ -6545,1685 +6580,1692 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>deepseek vs chatgpt for data analysis</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gemini vs chatgpt for data analysis</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>good kpi dashboard</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>good vs bad dashboard design</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>grok vs chatgpt for data analysis</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>how good is chatgpt for data analysis</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>how reliable is chatgpt for data analysis</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>how to comment power bi dax</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>how to concatenate in power bi dax</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in excel from scratch</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in google sheets</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in excel</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in power bi</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in tableau</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>how to dashboard design</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>how to design kpi dashboard</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>how to divide in power bi dax</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>how to learn power bi dax</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>how to multiply in power bi dax</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>how to open power bi dax</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>how to power bi dax</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>how to practice power bi dax</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis in excel</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>how to use power bi dax</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>how to write power bi dax</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>if or power bi dax</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>julius ai vs chatgpt for data analysis</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>julius vs chatgpt for data analysis</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kpi dashboard</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kpi dashboard design</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kpi dashboard examples</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kpi dashboard excel</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kpi dashboard ideas</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kpi dashboard meaning</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kpi dashboard power bi</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kpi dashboard template</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kpi dashboard template excel</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>llm for bi</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>perplexity vs chatgpt for data analysis</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>perplexity vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi courses</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>power bi dax</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>power bi dax best practices</t>
+          <t>power bi dax</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>power bi dax cheat sheet</t>
+          <t>power bi dax best practices</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>power bi dax filter</t>
+          <t>power bi dax cheat sheet</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>power bi dax functions</t>
+          <t>power bi dax filter</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>power bi dax functions list</t>
+          <t>power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>power bi dax if statement</t>
+          <t>power bi dax functions list</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>power bi dax queries</t>
+          <t>power bi dax if statement</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>power bi dax query view</t>
+          <t>power bi dax queries</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>power bi dax switch</t>
+          <t>power bi dax query view</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>power bi dax tutorial</t>
+          <t>power bi dax switch</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>power bi dax vs power query</t>
+          <t>power bi dax tutorial</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi dax vs power query</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>power bi vs power bi dax</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>power bi vs power bi dax</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>stakeholder reporting</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>stakeholder reporting forvis mazars</t>
+          <t>stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh</t>
+          <t>stakeholder reporting forvis mazars</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh &amp; co kg</t>
+          <t>stakeholder reporting gmbh</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>stakeholder reporting hamburg</t>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>stakeholder reporting meaning</t>
+          <t>stakeholder reporting hamburg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>stakeholder reporting template</t>
+          <t>stakeholder reporting meaning</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>stakeholder reporting template</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>top 10 power bi dax</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>top 5 power bi dax</t>
+          <t>top 10 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>top 5 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>top kpi dashboard</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>top n power bi dax</t>
+          <t>top kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>top power bi dax functions</t>
+          <t>top n power bi dax</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>top power bi dax interview questions</t>
+          <t>top power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>types of dashboard design</t>
+          <t>top power bi dax interview questions</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>using chatgpt for data analysis</t>
+          <t>types of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>using chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>what is a floating element in tableau dashboard design</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>what is a good dashboard design</t>
+          <t>what is a floating element in tableau dashboard design</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is a good dashboard design</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>what is bi dashboard design</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>what is dashboard design</t>
+          <t>what is bi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is dashboard design</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>what is kpi dashboard</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>what is kpi dashboard development</t>
+          <t>what is kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in excel</t>
+          <t>what is kpi dashboard development</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in power bi</t>
+          <t>what is kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in tableau</t>
+          <t>what is kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>what is power bi dax</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>what is power bi dax code</t>
+          <t>what is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>what is power bi dax function</t>
+          <t>what is power bi dax code</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>what is power bi dax measures</t>
+          <t>what is power bi dax function</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>what is power bi dax query</t>
+          <t>what is power bi dax measures</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>what is power bi dax studio</t>
+          <t>what is power bi dax query</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>what is power bi dax used for</t>
+          <t>what is power bi dax studio</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi dax used for</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>what is saas dashboard design</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>what is stakeholder reporting</t>
+          <t>what is saas dashboard design</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>what is the best chatgpt for data analysis</t>
+          <t>what is stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>what is the best version of chatgpt for data analysis</t>
+          <t>what is the best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>what is the fundamental challenge of dashboard design</t>
+          <t>what is the best version of chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>what language is power bi dax</t>
+          <t>what is the fundamental challenge of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what language is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>
